--- a/api/clv2/xlsx/fr/IATIOrganisationIdentifier.xlsx
+++ b/api/clv2/xlsx/fr/IATIOrganisationIdentifier.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="82">
   <si>
     <t>code</t>
   </si>
@@ -64,12 +64,24 @@
     <t>http://www.aias.gov.mz/</t>
   </si>
   <si>
+    <t>XI-IATI-AJS</t>
+  </si>
+  <si>
+    <t>http://www.femmesjuristes.org</t>
+  </si>
+  <si>
     <t>XI-IATI-ATTIC</t>
   </si>
   <si>
     <t>Website is still in progress</t>
   </si>
   <si>
+    <t>XI-IATI-BBDN</t>
+  </si>
+  <si>
+    <t>https://www.bbdn.com.bd/</t>
+  </si>
+  <si>
     <t>XI-IATI-EBRD</t>
   </si>
   <si>
@@ -166,6 +178,12 @@
     <t>https://www.international-climate-initiative.com/</t>
   </si>
   <si>
+    <t>XI-IATI-KHF</t>
+  </si>
+  <si>
+    <t>http://www.kinghusseinfoundation.org/</t>
+  </si>
+  <si>
     <t>XI-IATI-LPI</t>
   </si>
   <si>
@@ -230,6 +248,18 @@
   </si>
   <si>
     <t>http://wash-alliance.org/</t>
+  </si>
+  <si>
+    <t>XI-IATI-WBTF</t>
+  </si>
+  <si>
+    <t>https://www.worldbank.org/en/publication/trust-fund-annual-report-2019</t>
+  </si>
+  <si>
+    <t>XI-IATI-WVDRC</t>
+  </si>
+  <si>
+    <t>https://www.wvi.org/congo-drc/about-us</t>
   </si>
 </sst>
 </file>
@@ -574,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -658,7 +688,7 @@
       <c r="A8" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
@@ -669,7 +699,7 @@
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
@@ -911,7 +941,7 @@
       <c r="A31" t="s">
         <v>62</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C31" t="s">
@@ -944,7 +974,7 @@
       <c r="A34" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>69</v>
       </c>
       <c r="C34" t="s">
@@ -959,6 +989,61 @@
         <v>71</v>
       </c>
       <c r="C35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>72</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>74</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" t="s">
         <v>5</v>
       </c>
     </row>
@@ -970,7 +1055,7 @@
     <hyperlink ref="B5" r:id="rId4"/>
     <hyperlink ref="B6" r:id="rId5"/>
     <hyperlink ref="B7" r:id="rId6"/>
-    <hyperlink ref="B9" r:id="rId7"/>
+    <hyperlink ref="B8" r:id="rId7"/>
     <hyperlink ref="B10" r:id="rId8"/>
     <hyperlink ref="B11" r:id="rId9"/>
     <hyperlink ref="B12" r:id="rId10"/>
@@ -992,10 +1077,15 @@
     <hyperlink ref="B28" r:id="rId26"/>
     <hyperlink ref="B29" r:id="rId27"/>
     <hyperlink ref="B30" r:id="rId28"/>
-    <hyperlink ref="B32" r:id="rId29"/>
-    <hyperlink ref="B33" r:id="rId30"/>
-    <hyperlink ref="B34" r:id="rId31"/>
+    <hyperlink ref="B31" r:id="rId29"/>
+    <hyperlink ref="B32" r:id="rId30"/>
+    <hyperlink ref="B33" r:id="rId31"/>
     <hyperlink ref="B35" r:id="rId32"/>
+    <hyperlink ref="B36" r:id="rId33"/>
+    <hyperlink ref="B37" r:id="rId34"/>
+    <hyperlink ref="B38" r:id="rId35"/>
+    <hyperlink ref="B39" r:id="rId36"/>
+    <hyperlink ref="B40" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
